--- a/ig/nr-add-jurisdiction/StructureDefinition-mesures-number-of-days.xlsx
+++ b/ig/nr-add-jurisdiction/StructureDefinition-mesures-number-of-days.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-20T12:14:51+00:00</t>
+    <t>2023-10-20T12:17:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
